--- a/문서/gameData.xlsx
+++ b/문서/gameData.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.286.56066"/>
+  <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="580" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="570" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,8 +16,15 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors/>
+  <commentList/>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>idx</t>
   </si>
@@ -38,6 +45,84 @@
   </si>
   <si>
     <t>CONTINUE</t>
+  </si>
+  <si>
+    <t>itemId</t>
+  </si>
+  <si>
+    <t>itemName</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>equipmentType</t>
+  </si>
+  <si>
+    <t>canStack</t>
+  </si>
+  <si>
+    <t>maxStackAmount</t>
+  </si>
+  <si>
+    <t>healAmount</t>
+  </si>
+  <si>
+    <t>itemNameId</t>
+  </si>
+  <si>
+    <t>소드</t>
+  </si>
+  <si>
+    <t>자수정 방패</t>
+  </si>
+  <si>
+    <t>attackDamage</t>
+  </si>
+  <si>
+    <t>attackSpeed</t>
+  </si>
+  <si>
+    <t>attackRange</t>
+  </si>
+  <si>
+    <t>iconKey</t>
+  </si>
+  <si>
+    <t>dropPrefabKey</t>
+  </si>
+  <si>
+    <t>equipPrefabKey</t>
+  </si>
+  <si>
+    <t>Sword_Equip</t>
+  </si>
+  <si>
+    <t>Sword_Drop</t>
+  </si>
+  <si>
+    <t>AmethystShield_Equip</t>
+  </si>
+  <si>
+    <t>AmethystShield_Drop</t>
+  </si>
+  <si>
+    <t>Sword_Icon</t>
+  </si>
+  <si>
+    <t>AmethystShield_Icon</t>
+  </si>
+  <si>
+    <t>itemKey</t>
+  </si>
+  <si>
+    <t>Sword</t>
+  </si>
+  <si>
+    <t>AmethystShield</t>
   </si>
 </sst>
 </file>
@@ -368,25 +453,21 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <bottom style="thick">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <bottom style="thick">
         <color rgb="FFACCCEA"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <bottom style="medium">
         <color theme="4" tint="0.399980"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -401,7 +482,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -416,7 +496,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -431,13 +510,11 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <top style="thin">
@@ -446,7 +523,6 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
@@ -598,12 +674,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -923,141 +1002,284 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultRowHeight="16.500000"/>
   <cols>
-    <col min="1" max="1" width="14.00500011" customWidth="1" outlineLevel="0"/>
-    <col min="2" max="3" width="40.63000107" customWidth="1" outlineLevel="0"/>
+    <col min="1" max="10" style="1" width="25.62999916" customWidth="1" outlineLevel="0"/>
+    <col min="11" max="17" style="1" width="20.62999916" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="1">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="1">
+        <v>20001</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="1">
+        <v>2</v>
+      </c>
+      <c r="G2" s="1">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="M2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="1">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="1">
+        <v>20002</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1">
-        <v>10000</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1">
-        <v>10001</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1">
+        <v>0</v>
+      </c>
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1">
-        <v>10002</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-    </row>
-    <row r="5" spans="1:3">
+        <v>1003</v>
+      </c>
+      <c r="C4" s="1">
+        <v>20003</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
-        <v>10003</v>
-      </c>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:3">
+        <v>1004</v>
+      </c>
+      <c r="C5" s="1">
+        <v>20004</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
-        <v>10004</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:3">
+        <v>1005</v>
+      </c>
+      <c r="C6" s="1">
+        <v>20005</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
-        <v>10005</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:3">
+        <v>1006</v>
+      </c>
+      <c r="C7" s="1">
+        <v>20006</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="1">
-        <v>10006</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:3">
+        <v>1007</v>
+      </c>
+      <c r="C8" s="1">
+        <v>20007</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="1">
-        <v>10007</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:3">
+        <v>1008</v>
+      </c>
+      <c r="C9" s="1">
+        <v>20008</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="1">
-        <v>10008</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:3">
+        <v>1009</v>
+      </c>
+      <c r="C10" s="1">
+        <v>20009</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" s="1">
-        <v>10009</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:3">
+        <v>1010</v>
+      </c>
+      <c r="C11" s="1">
+        <v>20010</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" s="1">
-        <v>10010</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:3">
+        <v>1011</v>
+      </c>
+      <c r="C12" s="1">
+        <v>20011</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" s="1">
-        <v>10011</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:3">
+        <v>1012</v>
+      </c>
+      <c r="C13" s="1">
+        <v>20012</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" s="1">
-        <v>10012</v>
-      </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-    </row>
-    <row r="15" spans="1:3">
+        <v>1013</v>
+      </c>
+      <c r="C14" s="1">
+        <v>20013</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" s="1">
-        <v>10013</v>
-      </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-    </row>
-    <row r="16" spans="1:3">
+        <v>1014</v>
+      </c>
+      <c r="C15" s="1">
+        <v>20014</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" s="1">
-        <v>10014</v>
-      </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
+        <v>1015</v>
+      </c>
+      <c r="C16" s="1">
+        <v>20015</v>
+      </c>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70" right="0.70" top="0.75" bottom="0.75" header="0.30" footer="0.30"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/문서/gameData.xlsx
+++ b/문서/gameData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="570" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="560" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>idx</t>
   </si>
@@ -123,6 +123,12 @@
   </si>
   <si>
     <t>AmethystShield</t>
+  </si>
+  <si>
+    <t>isEquip</t>
+  </si>
+  <si>
+    <t>gridIdx</t>
   </si>
 </sst>
 </file>
@@ -1002,14 +1008,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr defaultRowHeight="16.500000"/>
+  <dimension ref="A1:S16"/>
+  <sheetFormatPr defaultColWidth="15.62500000" defaultRowHeight="16.500000"/>
   <cols>
-    <col min="1" max="10" style="1" width="25.62999916" customWidth="1" outlineLevel="0"/>
-    <col min="11" max="17" style="1" width="20.62999916" customWidth="1" outlineLevel="0"/>
+    <col min="1" max="19" style="1" width="15.63000011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1032,25 +1037,31 @@
         <v>11</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:15">
       <c r="A2" s="1">
         <v>1001</v>
       </c>
@@ -1076,22 +1087,28 @@
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="M2" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="O2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="1">
         <v>1002</v>
       </c>
@@ -1117,7 +1134,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" s="1">
         <v>0</v>
@@ -1131,8 +1148,14 @@
       <c r="M3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="1">
         <v>1003</v>
       </c>
@@ -1143,7 +1166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:15">
       <c r="A5" s="1">
         <v>1004</v>
       </c>
@@ -1154,7 +1177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:15">
       <c r="A6" s="1">
         <v>1005</v>
       </c>
@@ -1165,7 +1188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:15">
       <c r="A7" s="1">
         <v>1006</v>
       </c>
@@ -1176,7 +1199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:15">
       <c r="A8" s="1">
         <v>1007</v>
       </c>
@@ -1187,7 +1210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:15">
       <c r="A9" s="1">
         <v>1008</v>
       </c>
@@ -1198,7 +1221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:15">
       <c r="A10" s="1">
         <v>1009</v>
       </c>
@@ -1209,7 +1232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:15">
       <c r="A11" s="1">
         <v>1010</v>
       </c>
@@ -1220,7 +1243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:15">
       <c r="A12" s="1">
         <v>1011</v>
       </c>
@@ -1231,7 +1254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:15">
       <c r="A13" s="1">
         <v>1012</v>
       </c>
@@ -1242,7 +1265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:15">
       <c r="A14" s="1">
         <v>1013</v>
       </c>
@@ -1253,7 +1276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:15">
       <c r="A15" s="1">
         <v>1014</v>
       </c>
@@ -1264,7 +1287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:15">
       <c r="A16" s="1">
         <v>1015</v>
       </c>

--- a/문서/gameData.xlsx
+++ b/문서/gameData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="560" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="550" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1008,7 +1008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr defaultColWidth="15.62500000" defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="19" style="1" width="15.63000011" customWidth="1" outlineLevel="0"/>
@@ -1295,6 +1295,53 @@
         <v>20015</v>
       </c>
       <c r="D16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="1">
+        <v>2001</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="1">
+        <v>20002</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="1">
+        <v>2</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0</v>
+      </c>
+      <c r="I17" s="1">
+        <v>2</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>0</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
         <v>0</v>
       </c>
     </row>

--- a/문서/gameData.xlsx
+++ b/문서/gameData.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>idx</t>
   </si>
@@ -129,6 +129,15 @@
   </si>
   <si>
     <t>gridIdx</t>
+  </si>
+  <si>
+    <t>itemExplanation</t>
+  </si>
+  <si>
+    <t>단단한 자수정으로 만들어져 방어력이 뛰어나다.</t>
+  </si>
+  <si>
+    <t>모험가에게 가장 기본적으로 필요한 무기 중 하나.</t>
   </si>
 </sst>
 </file>
@@ -1052,14 +1061,10 @@
         <v>14</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1">
@@ -1098,15 +1103,11 @@
       <c r="L2" s="1">
         <v>0</v>
       </c>
-      <c r="M2" s="1">
-        <v>1</v>
-      </c>
-      <c r="N2" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="O2" s="1">
-        <v>1</v>
-      </c>
+      <c r="M2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="1">
@@ -1145,15 +1146,9 @@
       <c r="L3" s="1">
         <v>0</v>
       </c>
-      <c r="M3" s="1">
-        <v>0</v>
-      </c>
-      <c r="N3" s="1">
-        <v>0</v>
-      </c>
-      <c r="O3" s="1">
-        <v>0</v>
-      </c>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="1">
@@ -1335,15 +1330,11 @@
       <c r="L17" s="1">
         <v>0</v>
       </c>
-      <c r="M17" s="1">
-        <v>0</v>
-      </c>
-      <c r="N17" s="1">
-        <v>0</v>
-      </c>
-      <c r="O17" s="1">
-        <v>0</v>
-      </c>
+      <c r="M17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/문서/gameData.xlsx
+++ b/문서/gameData.xlsx
@@ -1023,7 +1023,7 @@
     <col min="1" max="19" style="1" width="15.63000011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1063,10 +1063,8 @@
       <c r="M1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-    </row>
-    <row r="2" spans="1:15">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="1">
         <v>1001</v>
       </c>
@@ -1106,10 +1104,8 @@
       <c r="M2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-    </row>
-    <row r="3" spans="1:15">
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="1">
         <v>1002</v>
       </c>
@@ -1146,11 +1142,8 @@
       <c r="L3" s="1">
         <v>0</v>
       </c>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-    </row>
-    <row r="4" spans="1:15">
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="1">
         <v>1003</v>
       </c>
@@ -1161,7 +1154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>1004</v>
       </c>
@@ -1172,7 +1165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>1005</v>
       </c>
@@ -1183,7 +1176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
         <v>1006</v>
       </c>
@@ -1194,7 +1187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:13">
       <c r="A8" s="1">
         <v>1007</v>
       </c>
@@ -1205,7 +1198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:13">
       <c r="A9" s="1">
         <v>1008</v>
       </c>
@@ -1216,7 +1209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:13">
       <c r="A10" s="1">
         <v>1009</v>
       </c>
@@ -1227,7 +1220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:13">
       <c r="A11" s="1">
         <v>1010</v>
       </c>
@@ -1238,7 +1231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:13">
       <c r="A12" s="1">
         <v>1011</v>
       </c>
@@ -1249,7 +1242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:13">
       <c r="A13" s="1">
         <v>1012</v>
       </c>
@@ -1260,7 +1253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:13">
       <c r="A14" s="1">
         <v>1013</v>
       </c>
@@ -1271,7 +1264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:13">
       <c r="A15" s="1">
         <v>1014</v>
       </c>
@@ -1282,7 +1275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:13">
       <c r="A16" s="1">
         <v>1015</v>
       </c>
@@ -1293,7 +1286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:13">
       <c r="A17" s="1">
         <v>2001</v>
       </c>
@@ -1333,8 +1326,6 @@
       <c r="M17" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/문서/gameData.xlsx
+++ b/문서/gameData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="550" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="540" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>idx</t>
   </si>
@@ -138,6 +138,9 @@
   </si>
   <si>
     <t>모험가에게 가장 기본적으로 필요한 무기 중 하나.</t>
+  </si>
+  <si>
+    <t>itemRarity</t>
   </si>
 </sst>
 </file>
@@ -1017,13 +1020,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultColWidth="15.62500000" defaultRowHeight="16.500000"/>
   <cols>
-    <col min="1" max="19" style="1" width="15.63000011" customWidth="1" outlineLevel="0"/>
+    <col min="1" max="5" style="1" width="15.63000011" customWidth="1" outlineLevel="0"/>
+    <col min="6" max="6" style="1" width="15.63000011" customWidth="1" outlineLevel="0"/>
+    <col min="7" max="14" style="1" width="15.63000011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1040,31 +1045,34 @@
         <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="1">
         <v>1001</v>
       </c>
@@ -1081,31 +1089,34 @@
         <v>31</v>
       </c>
       <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
         <v>2</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>1</v>
       </c>
-      <c r="H2" s="1">
-        <v>0</v>
-      </c>
       <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
         <v>1</v>
       </c>
-      <c r="J2" s="1">
-        <v>0</v>
-      </c>
       <c r="K2" s="1">
         <v>0</v>
       </c>
       <c r="L2" s="1">
         <v>0</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="1">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14">
       <c r="A3" s="1">
         <v>1002</v>
       </c>
@@ -1122,28 +1133,31 @@
         <v>32</v>
       </c>
       <c r="F3" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
         <v>2</v>
       </c>
       <c r="H3" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
         <v>2</v>
       </c>
-      <c r="J3" s="1">
-        <v>0</v>
-      </c>
       <c r="K3" s="1">
         <v>0</v>
       </c>
       <c r="L3" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="M3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="1">
         <v>1003</v>
       </c>
@@ -1153,8 +1167,11 @@
       <c r="D4" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="1">
         <v>1004</v>
       </c>
@@ -1164,8 +1181,11 @@
       <c r="D5" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="1">
         <v>1005</v>
       </c>
@@ -1175,8 +1195,11 @@
       <c r="D6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="1">
         <v>1006</v>
       </c>
@@ -1186,8 +1209,11 @@
       <c r="D7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="1">
         <v>1007</v>
       </c>
@@ -1197,8 +1223,11 @@
       <c r="D8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="1">
         <v>1008</v>
       </c>
@@ -1208,8 +1237,11 @@
       <c r="D9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="1">
         <v>1009</v>
       </c>
@@ -1219,8 +1251,11 @@
       <c r="D10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="1">
         <v>1010</v>
       </c>
@@ -1230,8 +1265,11 @@
       <c r="D11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="1">
         <v>1011</v>
       </c>
@@ -1241,8 +1279,11 @@
       <c r="D12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="1">
         <v>1012</v>
       </c>
@@ -1252,8 +1293,11 @@
       <c r="D13" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="1">
         <v>1013</v>
       </c>
@@ -1263,8 +1307,11 @@
       <c r="D14" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="1">
         <v>1014</v>
       </c>
@@ -1274,8 +1321,11 @@
       <c r="D15" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="1">
         <v>1015</v>
       </c>
@@ -1285,8 +1335,11 @@
       <c r="D16" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="1">
         <v>2001</v>
       </c>
@@ -1303,27 +1356,30 @@
         <v>32</v>
       </c>
       <c r="F17" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
         <v>2</v>
       </c>
       <c r="H17" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" s="1">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1">
         <v>2</v>
       </c>
-      <c r="J17" s="1">
-        <v>0</v>
-      </c>
       <c r="K17" s="1">
         <v>0</v>
       </c>
       <c r="L17" s="1">
         <v>0</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1" t="s">
         <v>36</v>
       </c>
     </row>

--- a/문서/gameData.xlsx
+++ b/문서/gameData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="Polaris Office Sheet" lastEdited="4" lowestEdited="4" rupBuild="10.105.307.56236"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="540" activeTab="0"/>
+    <workbookView xWindow="360" yWindow="30" windowWidth="25755" windowHeight="11595" tabRatio="530" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>idx</t>
   </si>
@@ -141,6 +141,18 @@
   </si>
   <si>
     <t>itemRarity</t>
+  </si>
+  <si>
+    <t>잿불가지</t>
+  </si>
+  <si>
+    <t>화염 덩굴</t>
+  </si>
+  <si>
+    <t>Infernal_Vine</t>
+  </si>
+  <si>
+    <t>Ember_Branch</t>
   </si>
 </sst>
 </file>
@@ -1020,12 +1032,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="15.62500000" defaultRowHeight="16.500000"/>
   <cols>
-    <col min="1" max="5" style="1" width="15.63000011" customWidth="1" outlineLevel="0"/>
-    <col min="6" max="6" style="1" width="15.63000011" customWidth="1" outlineLevel="0"/>
-    <col min="7" max="14" style="1" width="15.63000011" customWidth="1" outlineLevel="0"/>
+    <col min="1" max="14" style="1" width="15.63000011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -1381,6 +1391,88 @@
       </c>
       <c r="N17" s="1" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="1">
+        <v>5000</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="1">
+        <v>0</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <v>0</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="1">
+        <v>7000</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="1">
+        <v>3</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2</v>
+      </c>
+      <c r="H19" s="1">
+        <v>3</v>
+      </c>
+      <c r="I19" s="1">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
+        <v>0</v>
+      </c>
+      <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
